--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92556615051</v>
+        <v>46157.93117765131</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93117765131</v>
+        <v>46157.93139751127</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93139751127</v>
+        <v>46157.93386467874</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93386467874</v>
+        <v>46157.93698296212</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93698296212</v>
+        <v>46158.28206166431</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28206166431</v>
+        <v>46158.29655200997</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29655200997</v>
+        <v>46158.29810331074</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29810331074</v>
+        <v>46158.33372485032</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33372485032</v>
+        <v>46158.37225029839</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37225029839</v>
+        <v>46158.37276758732</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
